--- a/PracticeList.xlsx
+++ b/PracticeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lxie1/personal/codingpractice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F72DB6BC-F33B-EF46-9FF0-50BE5AA6202C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37758A54-DAB7-4D45-A2E3-F08AA7B74ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1380" windowWidth="30240" windowHeight="17580" xr2:uid="{7D075F38-A8A9-0349-9089-EC4AFD30F784}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="555">
   <si>
     <t>LinkedList</t>
   </si>
@@ -1809,6 +1809,15 @@
   </si>
   <si>
     <t>76/438/567 模板</t>
+  </si>
+  <si>
+    <t>子数组类 DP 总结总模板 (53、152、918)</t>
+  </si>
+  <si>
+    <t>740稀疏背包问题！！！416 固定capacity 0/1 背包问题 + 可行判断=dp！！！39=完全背包+枚举所有可能=backtracking！！！40=0/1背包+去重+枚举=backtracking！！！</t>
+  </si>
+  <si>
+    <t>🌟399</t>
   </si>
 </sst>
 </file>
@@ -3302,7 +3311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4AC671-66B9-9043-8EF5-2D6A00DBDF6A}">
-  <dimension ref="A1:T78"/>
+  <dimension ref="A1:T80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3492,7 +3501,7 @@
       <c r="Q3" s="217">
         <v>67</v>
       </c>
-      <c r="R3">
+      <c r="R3" s="221">
         <v>3333</v>
       </c>
     </row>
@@ -3553,7 +3562,7 @@
       </c>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="217">
+      <c r="A5" s="220">
         <v>31</v>
       </c>
       <c r="B5" s="220">
@@ -3580,7 +3589,7 @@
       <c r="I5" s="220" t="s">
         <v>95</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="221" t="s">
         <v>85</v>
       </c>
       <c r="K5" s="221" t="s">
@@ -3589,19 +3598,19 @@
       <c r="L5" s="221" t="s">
         <v>72</v>
       </c>
-      <c r="M5" s="217">
+      <c r="M5" s="221">
         <v>5</v>
       </c>
       <c r="N5" s="220">
         <v>127</v>
       </c>
-      <c r="O5" s="217">
+      <c r="O5" s="220">
         <v>22</v>
       </c>
       <c r="P5" s="221">
         <v>391</v>
       </c>
-      <c r="Q5" s="217">
+      <c r="Q5" s="221">
         <v>9</v>
       </c>
       <c r="R5">
@@ -3651,7 +3660,7 @@
       <c r="N6">
         <v>1293</v>
       </c>
-      <c r="O6" s="217">
+      <c r="O6" s="220">
         <v>17</v>
       </c>
       <c r="P6" s="221">
@@ -3710,7 +3719,7 @@
       <c r="Q7" s="220">
         <v>48</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="221">
         <v>3147</v>
       </c>
     </row>
@@ -3751,7 +3760,7 @@
       <c r="O8" s="217">
         <v>10</v>
       </c>
-      <c r="Q8" s="217">
+      <c r="Q8" s="221">
         <v>7</v>
       </c>
       <c r="R8">
@@ -3789,8 +3798,8 @@
       <c r="M9" s="1">
         <v>926</v>
       </c>
-      <c r="N9" s="1">
-        <v>399</v>
+      <c r="N9" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="O9" s="221">
         <v>78</v>
@@ -3912,7 +3921,7 @@
       <c r="M12" s="1">
         <v>322</v>
       </c>
-      <c r="N12" s="1">
+      <c r="N12" s="221">
         <v>286</v>
       </c>
       <c r="O12">
@@ -3985,7 +3994,7 @@
       <c r="I14" s="221" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M14" s="221">
         <v>740</v>
       </c>
       <c r="N14" s="220">
@@ -4002,7 +4011,7 @@
       <c r="A15" s="221">
         <v>881</v>
       </c>
-      <c r="B15" s="217">
+      <c r="B15" s="221">
         <v>658</v>
       </c>
       <c r="D15" s="221">
@@ -4139,7 +4148,7 @@
       </c>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="217">
+      <c r="A19" s="221">
         <v>189</v>
       </c>
       <c r="B19">
@@ -4227,7 +4236,7 @@
       <c r="M21" s="220">
         <v>118</v>
       </c>
-      <c r="N21" s="1">
+      <c r="N21" s="221">
         <v>419</v>
       </c>
       <c r="O21" s="221">
@@ -4253,7 +4262,7 @@
       <c r="I22" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="M22" s="217">
+      <c r="M22" s="221">
         <v>152</v>
       </c>
       <c r="N22" s="220">
@@ -4293,7 +4302,7 @@
       <c r="A24" s="220">
         <v>202</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="221">
         <v>2008</v>
       </c>
       <c r="D24" s="220">
@@ -4382,7 +4391,7 @@
       <c r="I28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M28" s="221">
         <v>416</v>
       </c>
     </row>
@@ -4676,7 +4685,7 @@
       </c>
       <c r="N57">
         <f>COUNT(N2:N25)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O57">
         <f>COUNT(O2:O22)</f>
@@ -4696,15 +4705,15 @@
       </c>
       <c r="S57">
         <f>SUM(A57:R57)</f>
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="58" spans="1:19">
       <c r="A58">
+        <v>17</v>
+      </c>
+      <c r="B58">
         <v>15</v>
-      </c>
-      <c r="B58">
-        <v>13</v>
       </c>
       <c r="C58">
         <v>6</v>
@@ -4725,10 +4734,10 @@
         <v>8</v>
       </c>
       <c r="I58">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K58">
         <v>2</v>
@@ -4737,36 +4746,36 @@
         <v>3</v>
       </c>
       <c r="M58">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N58">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O58">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P58">
         <v>2</v>
       </c>
       <c r="Q58">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S58">
         <f>SUM(A58:R58)</f>
-        <v>148</v>
+        <v>167</v>
       </c>
     </row>
     <row r="59" spans="1:19">
       <c r="A59">
         <f>A58/A57</f>
-        <v>0.46875</v>
+        <v>0.53125</v>
       </c>
       <c r="B59">
         <f>B58/B57</f>
-        <v>0.44827586206896552</v>
+        <v>0.51724137931034486</v>
       </c>
       <c r="C59">
         <f t="shared" ref="C59:G59" si="0">C58/C57</f>
@@ -4794,11 +4803,11 @@
       </c>
       <c r="I59">
         <f t="shared" ref="I59" si="1">I58/I57</f>
-        <v>0.36363636363636365</v>
+        <v>0.4</v>
       </c>
       <c r="J59">
         <f t="shared" ref="J59" si="2">J58/J57</f>
-        <v>0.33333333333333331</v>
+        <v>0.5</v>
       </c>
       <c r="K59">
         <f>K58/K57</f>
@@ -4810,15 +4819,15 @@
       </c>
       <c r="M59">
         <f t="shared" ref="M59" si="4">M58/M57</f>
-        <v>0.31818181818181818</v>
+        <v>0.40909090909090912</v>
       </c>
       <c r="N59">
         <f t="shared" ref="N59" si="5">N58/N57</f>
-        <v>0.33333333333333331</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="O59">
         <f t="shared" ref="O59" si="6">O58/O57</f>
-        <v>0.33333333333333331</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="P59">
         <f t="shared" ref="P59" si="7">P58/P57</f>
@@ -4826,15 +4835,15 @@
       </c>
       <c r="Q59">
         <f>Q58/Q57</f>
-        <v>0.375</v>
+        <v>0.45833333333333331</v>
       </c>
       <c r="R59">
         <f t="shared" ref="R59" si="8">R58/R57</f>
-        <v>0.22222222222222221</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="S59">
         <f t="shared" ref="S59" si="9">S58/S57</f>
-        <v>0.39257294429708223</v>
+        <v>0.44414893617021278</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4925,6 +4934,16 @@
     <row r="78" spans="1:1">
       <c r="A78" t="s">
         <v>551</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>553</v>
       </c>
     </row>
   </sheetData>

--- a/PracticeList.xlsx
+++ b/PracticeList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lxie1/personal/codingpractice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37758A54-DAB7-4D45-A2E3-F08AA7B74ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C122A097-D14E-BF4D-A369-686895DFF824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1380" windowWidth="30240" windowHeight="17580" xr2:uid="{7D075F38-A8A9-0349-9089-EC4AFD30F784}"/>
+    <workbookView xWindow="0" yWindow="2060" windowWidth="30240" windowHeight="17580" xr2:uid="{7D075F38-A8A9-0349-9089-EC4AFD30F784}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="562">
   <si>
     <t>LinkedList</t>
   </si>
@@ -1819,12 +1819,55 @@
   <si>
     <t>🌟399</t>
   </si>
+  <si>
+    <t>总结快慢指针截止条件和奇偶数长度和slow指针最后位置关系，以lc234为例！</t>
+  </si>
+  <si>
+    <t>lc421 -&gt;  int maxLen = Integer.toBinaryString(maxNum).length();</t>
+  </si>
+  <si>
+    <t>/******************** Solution 3: A* Search ************************/</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">// </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="Menlo-Regular"/>
+        <family val="3"/>
+      </rPr>
+      <t>还没看！！！</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9.8000000000000007"/>
+        <color rgb="FF8C8C8C"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+      </rPr>
+      <t>https://leetcode.com/problems/shortest-path-in-binary-matrix/solution/</t>
+    </r>
+  </si>
+  <si>
+    <t>lc986 res.toArray(new int[res.size()][2])</t>
+  </si>
+  <si>
+    <t>lc875 整除向上下取整技巧</t>
+  </si>
+  <si>
+    <t>lc878 gcd, lcm, 1-x中多少个a或b的倍数～</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1909,6 +1952,20 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Menlo-Regular"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2375,7 +2432,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2936,6 +2993,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2999,8 +3057,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFC96FF1"/>
       <color rgb="FFE1BBEE"/>
-      <color rgb="FFC96FF1"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3311,7 +3369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C4AC671-66B9-9043-8EF5-2D6A00DBDF6A}">
-  <dimension ref="A1:T80"/>
+  <dimension ref="A1:T86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -3400,7 +3458,7 @@
       <c r="C2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="217">
+      <c r="D2" s="220">
         <v>1</v>
       </c>
       <c r="E2" s="1">
@@ -3412,7 +3470,7 @@
       <c r="G2" s="220">
         <v>346</v>
       </c>
-      <c r="H2" s="217">
+      <c r="H2" s="220">
         <v>3</v>
       </c>
       <c r="I2" s="220" t="s">
@@ -3433,7 +3491,7 @@
       <c r="N2" s="220">
         <v>200</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="220">
         <v>273</v>
       </c>
       <c r="P2">
@@ -3459,7 +3517,7 @@
       <c r="C3" s="220" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="221">
         <v>560</v>
       </c>
       <c r="E3" s="220">
@@ -3498,7 +3556,7 @@
       <c r="P3">
         <v>850</v>
       </c>
-      <c r="Q3" s="217">
+      <c r="Q3" s="220">
         <v>67</v>
       </c>
       <c r="R3" s="221">
@@ -3548,13 +3606,13 @@
       <c r="N4" s="1">
         <v>815</v>
       </c>
-      <c r="O4" s="214">
+      <c r="O4" s="220">
         <v>79</v>
       </c>
       <c r="P4">
         <v>1851</v>
       </c>
-      <c r="Q4" s="217">
+      <c r="Q4" s="221">
         <v>29</v>
       </c>
       <c r="R4">
@@ -3571,7 +3629,7 @@
       <c r="C5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="217">
+      <c r="D5" s="221">
         <v>423</v>
       </c>
       <c r="E5" s="220">
@@ -3648,10 +3706,10 @@
       <c r="J6" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="K6" s="220" t="s">
         <v>76</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="221" t="s">
         <v>89</v>
       </c>
       <c r="M6" s="1">
@@ -3704,13 +3762,13 @@
       <c r="J7" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="220" t="s">
         <v>69</v>
       </c>
       <c r="M7" s="214">
         <v>312</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="220">
         <v>1091</v>
       </c>
       <c r="O7" s="214">
@@ -3730,10 +3788,10 @@
       <c r="B8" s="1">
         <v>410</v>
       </c>
-      <c r="C8" s="217" t="s">
+      <c r="C8" s="221" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="217">
+      <c r="D8" s="221">
         <v>380</v>
       </c>
       <c r="E8" s="220">
@@ -3751,7 +3809,7 @@
       <c r="L8" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8" s="221">
         <v>799</v>
       </c>
       <c r="N8">
@@ -3763,7 +3821,7 @@
       <c r="Q8" s="221">
         <v>7</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="221">
         <v>3354</v>
       </c>
     </row>
@@ -3774,13 +3832,13 @@
       <c r="B9" s="220">
         <v>362</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="220" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="1">
         <v>811</v>
       </c>
-      <c r="E9" s="217">
+      <c r="E9" s="221">
         <v>224</v>
       </c>
       <c r="F9" s="1">
@@ -3795,7 +3853,7 @@
       <c r="L9" s="212" t="s">
         <v>70</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="221">
         <v>926</v>
       </c>
       <c r="N9" s="1" t="s">
@@ -3842,7 +3900,7 @@
       <c r="M10" s="221">
         <v>198</v>
       </c>
-      <c r="N10" s="1">
+      <c r="N10" s="220">
         <v>529</v>
       </c>
       <c r="O10" s="212">
@@ -3859,7 +3917,7 @@
       <c r="A11" s="1">
         <v>923</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="220">
         <v>1011</v>
       </c>
       <c r="C11" s="221" t="s">
@@ -3956,7 +4014,7 @@
       <c r="I13" s="220" t="s">
         <v>52</v>
       </c>
-      <c r="M13" s="217">
+      <c r="M13" s="220">
         <v>70</v>
       </c>
       <c r="N13" s="1">
@@ -3973,7 +4031,7 @@
       <c r="A14" s="221">
         <v>532</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="221">
         <v>878</v>
       </c>
       <c r="C14" s="220" t="s">
@@ -4035,7 +4093,7 @@
       <c r="N15" s="1">
         <v>332</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="220">
         <v>51</v>
       </c>
       <c r="Q15">
@@ -4043,7 +4101,7 @@
       </c>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="1">
+      <c r="A16" s="221">
         <v>723</v>
       </c>
       <c r="B16" s="220">
@@ -4078,10 +4136,10 @@
       </c>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="1">
+      <c r="A17" s="221">
         <v>986</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="220">
         <v>875</v>
       </c>
       <c r="D17" s="1">
@@ -4215,7 +4273,7 @@
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="A21" s="1">
+      <c r="A21" s="221">
         <v>287</v>
       </c>
       <c r="B21">
@@ -4224,13 +4282,13 @@
       <c r="D21" s="220">
         <v>12</v>
       </c>
-      <c r="E21" s="214">
+      <c r="E21" s="220">
         <v>402</v>
       </c>
       <c r="F21" s="221">
         <v>220</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="220" t="s">
         <v>22</v>
       </c>
       <c r="M21" s="220">
@@ -4259,7 +4317,7 @@
       <c r="E22" s="221">
         <v>907</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="221" t="s">
         <v>150</v>
       </c>
       <c r="M22" s="221">
@@ -4285,7 +4343,7 @@
       <c r="D23" s="221">
         <v>301</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="221" t="s">
         <v>23</v>
       </c>
       <c r="M23" s="217">
@@ -4308,7 +4366,7 @@
       <c r="D24" s="220">
         <v>243</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="220" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="1">
@@ -4328,7 +4386,7 @@
       <c r="B25">
         <v>668</v>
       </c>
-      <c r="D25" s="217">
+      <c r="D25" s="221">
         <v>421</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -4357,8 +4415,11 @@
       <c r="I26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="217">
+      <c r="M26" s="220">
         <v>91</v>
+      </c>
+      <c r="Q26" s="221">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:17">
@@ -4385,7 +4446,7 @@
       <c r="B28" s="220">
         <v>35</v>
       </c>
-      <c r="D28" s="217">
+      <c r="D28" s="220">
         <v>387</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -4572,7 +4633,7 @@
       </c>
     </row>
     <row r="45" spans="1:13">
-      <c r="I45" s="217" t="s">
+      <c r="I45" s="220" t="s">
         <v>43</v>
       </c>
       <c r="M45" s="221">
@@ -4580,7 +4641,7 @@
       </c>
     </row>
     <row r="46" spans="1:13">
-      <c r="I46" s="217" t="s">
+      <c r="I46" s="220" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4710,19 +4771,19 @@
     </row>
     <row r="58" spans="1:19">
       <c r="A58">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B58">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C58">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D58">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E58">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F58">
         <v>10</v>
@@ -4731,63 +4792,63 @@
         <v>3</v>
       </c>
       <c r="H58">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I58">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J58">
         <v>3</v>
       </c>
       <c r="K58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M58">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N58">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O58">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P58">
         <v>2</v>
       </c>
       <c r="Q58">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S58">
         <f>SUM(A58:R58)</f>
-        <v>167</v>
+        <v>203</v>
       </c>
     </row>
     <row r="59" spans="1:19">
       <c r="A59">
         <f>A58/A57</f>
-        <v>0.53125</v>
+        <v>0.625</v>
       </c>
       <c r="B59">
         <f>B58/B57</f>
-        <v>0.51724137931034486</v>
+        <v>0.62068965517241381</v>
       </c>
       <c r="C59">
         <f t="shared" ref="C59:G59" si="0">C58/C57</f>
-        <v>0.46153846153846156</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="D59">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E59">
         <f t="shared" si="0"/>
-        <v>0.42857142857142855</v>
+        <v>0.52380952380952384</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
@@ -4799,11 +4860,11 @@
       </c>
       <c r="H59">
         <f>H58/H57</f>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="I59">
         <f t="shared" ref="I59" si="1">I58/I57</f>
-        <v>0.4</v>
+        <v>0.50909090909090904</v>
       </c>
       <c r="J59">
         <f t="shared" ref="J59" si="2">J58/J57</f>
@@ -4811,39 +4872,39 @@
       </c>
       <c r="K59">
         <f>K58/K57</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L59">
         <f t="shared" ref="L59" si="3">L58/L57</f>
-        <v>0.33333333333333331</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="M59">
         <f t="shared" ref="M59" si="4">M58/M57</f>
-        <v>0.40909090909090912</v>
+        <v>0.5</v>
       </c>
       <c r="N59">
         <f t="shared" ref="N59" si="5">N58/N57</f>
-        <v>0.43478260869565216</v>
+        <v>0.52173913043478259</v>
       </c>
       <c r="O59">
-        <f t="shared" ref="O59" si="6">O58/O57</f>
-        <v>0.42857142857142855</v>
+        <f>O58/O57</f>
+        <v>0.52380952380952384</v>
       </c>
       <c r="P59">
-        <f t="shared" ref="P59" si="7">P58/P57</f>
+        <f t="shared" ref="P59" si="6">P58/P57</f>
         <v>0.4</v>
       </c>
       <c r="Q59">
         <f>Q58/Q57</f>
-        <v>0.45833333333333331</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="R59">
-        <f t="shared" ref="R59" si="8">R58/R57</f>
-        <v>0.44444444444444442</v>
+        <f t="shared" ref="R59" si="7">R58/R57</f>
+        <v>0.55555555555555558</v>
       </c>
       <c r="S59">
-        <f t="shared" ref="S59" si="9">S58/S57</f>
-        <v>0.44414893617021278</v>
+        <f t="shared" ref="S59" si="8">S58/S57</f>
+        <v>0.53989361702127658</v>
       </c>
     </row>
     <row r="61" spans="1:19">
@@ -4944,6 +5005,39 @@
     <row r="80" spans="1:1">
       <c r="A80" t="s">
         <v>553</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="222" t="s">
+        <v>557</v>
+      </c>
+      <c r="C83" s="222" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -4976,13 +5070,13 @@
       <c r="B1" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="223" t="s">
+      <c r="C1" s="224" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="225"/>
       <c r="H1" s="14" t="s">
         <v>104</v>
       </c>
@@ -5117,13 +5211,13 @@
       <c r="B1" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="235" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="236"/>
       <c r="H1" s="82" t="s">
         <v>104</v>
       </c>
@@ -5371,13 +5465,13 @@
       <c r="B1" s="184" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="237" t="s">
+      <c r="C1" s="238" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
       <c r="J1" s="152"/>
       <c r="K1" s="130" t="s">
         <v>104</v>
@@ -5724,14 +5818,14 @@
       <c r="B1" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C1" s="222" t="s">
+      <c r="C1" s="223" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="224"/>
       <c r="I1" s="120"/>
       <c r="J1" s="121"/>
       <c r="K1" s="14" t="s">
@@ -6010,13 +6104,13 @@
       <c r="B1" s="128" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="238" t="s">
+      <c r="C1" s="239" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="227"/>
       <c r="H1" s="130" t="s">
         <v>104</v>
       </c>
@@ -6249,14 +6343,14 @@
       <c r="B1" s="129" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="225" t="s">
+      <c r="C1" s="226" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="239"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="225"/>
-      <c r="H1" s="226"/>
+      <c r="D1" s="240"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="227"/>
       <c r="I1" s="130" t="s">
         <v>104</v>
       </c>
@@ -6656,13 +6750,13 @@
       <c r="B1" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="235" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="236"/>
       <c r="H1" s="82" t="s">
         <v>104</v>
       </c>
@@ -6873,13 +6967,13 @@
       <c r="B1" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="C1" s="222" t="s">
+      <c r="C1" s="223" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="224"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="225"/>
       <c r="H1" s="14" t="s">
         <v>104</v>
       </c>
@@ -7015,13 +7109,13 @@
       <c r="B1" s="127" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="225" t="s">
+      <c r="C1" s="226" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="225"/>
-      <c r="E1" s="225"/>
-      <c r="F1" s="225"/>
-      <c r="G1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="227"/>
       <c r="H1" s="130" t="s">
         <v>104</v>
       </c>
@@ -7155,13 +7249,13 @@
       <c r="B1" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="227" t="s">
+      <c r="C1" s="228" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
       <c r="J1" s="39"/>
@@ -7330,19 +7424,19 @@
       <c r="K11" s="40"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="228" t="s">
+      <c r="A15" s="229" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="229"/>
-      <c r="C15" s="229"/>
-      <c r="D15" s="229"/>
-      <c r="E15" s="229"/>
-      <c r="F15" s="229"/>
-      <c r="G15" s="229"/>
-      <c r="H15" s="229"/>
-      <c r="I15" s="229"/>
-      <c r="J15" s="229"/>
-      <c r="K15" s="229"/>
+      <c r="B15" s="230"/>
+      <c r="C15" s="230"/>
+      <c r="D15" s="230"/>
+      <c r="E15" s="230"/>
+      <c r="F15" s="230"/>
+      <c r="G15" s="230"/>
+      <c r="H15" s="230"/>
+      <c r="I15" s="230"/>
+      <c r="J15" s="230"/>
+      <c r="K15" s="230"/>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="29" t="s">
@@ -7407,13 +7501,13 @@
       <c r="B1" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="230" t="s">
+      <c r="C1" s="231" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
-      <c r="G1" s="227"/>
+      <c r="D1" s="228"/>
+      <c r="E1" s="228"/>
+      <c r="F1" s="228"/>
+      <c r="G1" s="228"/>
       <c r="H1" s="38"/>
       <c r="I1" s="39"/>
       <c r="J1" s="28" t="s">
@@ -7618,14 +7712,14 @@
       <c r="B1" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="222" t="s">
+      <c r="C1" s="223" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="223"/>
-      <c r="E1" s="231"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="224"/>
+      <c r="D1" s="224"/>
+      <c r="E1" s="232"/>
+      <c r="F1" s="224"/>
+      <c r="G1" s="224"/>
+      <c r="H1" s="225"/>
       <c r="I1" s="14" t="s">
         <v>104</v>
       </c>
@@ -7779,14 +7873,14 @@
       <c r="B1" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="232" t="s">
+      <c r="C1" s="233" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="233"/>
-      <c r="E1" s="233"/>
-      <c r="F1" s="233"/>
-      <c r="G1" s="233"/>
-      <c r="H1" s="233"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
       <c r="I1" s="67"/>
       <c r="J1" s="67"/>
       <c r="K1" s="54" t="s">
@@ -8056,13 +8150,13 @@
       <c r="B1" s="81" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="234" t="s">
+      <c r="C1" s="235" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="236"/>
       <c r="H1" s="82" t="s">
         <v>104</v>
       </c>
@@ -8218,13 +8312,13 @@
       <c r="B1" s="156" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="236" t="s">
+      <c r="C1" s="237" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="236"/>
-      <c r="E1" s="236"/>
-      <c r="F1" s="236"/>
-      <c r="G1" s="236"/>
+      <c r="D1" s="237"/>
+      <c r="E1" s="237"/>
+      <c r="F1" s="237"/>
+      <c r="G1" s="237"/>
       <c r="H1" s="157"/>
       <c r="I1" s="158"/>
       <c r="J1" s="159" t="s">

--- a/PracticeList.xlsx
+++ b/PracticeList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lxie1/personal/codingpractice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C122A097-D14E-BF4D-A369-686895DFF824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFACBE66-C442-9B4B-A4BD-FFA1BA9D0069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2060" windowWidth="30240" windowHeight="17580" xr2:uid="{7D075F38-A8A9-0349-9089-EC4AFD30F784}"/>
   </bookViews>
@@ -3057,8 +3057,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFE1BBEE"/>
       <color rgb="FFC96FF1"/>
-      <color rgb="FFE1BBEE"/>
     </mruColors>
   </colors>
   <extLst>
@@ -3461,7 +3461,7 @@
       <c r="D2" s="220">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="221">
         <v>1249</v>
       </c>
       <c r="F2" s="221">
@@ -3741,7 +3741,7 @@
       <c r="C7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="220">
         <v>1570</v>
       </c>
       <c r="E7" s="1">
@@ -4780,10 +4780,10 @@
         <v>8</v>
       </c>
       <c r="D58">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E58">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F58">
         <v>10</v>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="S58">
         <f>SUM(A58:R58)</f>
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" spans="1:19">
@@ -4844,11 +4844,11 @@
       </c>
       <c r="D59">
         <f t="shared" si="0"/>
-        <v>0.55555555555555558</v>
+        <v>0.61111111111111116</v>
       </c>
       <c r="E59">
         <f t="shared" si="0"/>
-        <v>0.52380952380952384</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
@@ -4904,7 +4904,7 @@
       </c>
       <c r="S59">
         <f t="shared" ref="S59" si="8">S58/S57</f>
-        <v>0.53989361702127658</v>
+        <v>0.5478723404255319</v>
       </c>
     </row>
     <row r="61" spans="1:19">
